--- a/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
+++ b/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
+++ b/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2325,54 +2325,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>BOVA11.SA</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>bova11</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>bova11</t>
-        </is>
-      </c>
+          <t>comex_corrente_comercio_usd</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ETF brasileiro associado ao desempenho do Ibovespa.</t>
+          <t>Corrente mensal de comércio exterior brasileira.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>etf</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2382,74 +2378,70 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>^BVSP</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ibovespa</t>
+          <t>comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ibovespa</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Índice Ibovespa.</t>
+          <t>Valor mensal total das exportações brasileiras em dólares FOB.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2459,17 +2451,13 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q34" t="b">
@@ -2479,54 +2467,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>IVVB11.SA</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ivvb11</t>
+          <t>comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ivvb11</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ETF brasileiro com exposição ao índice S&amp;P 500.</t>
+          <t>Peso líquido mensal total das exportações brasileiras.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2536,17 +2520,13 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q35" t="b">
@@ -2556,51 +2536,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>BOVA11.SA</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ret_bova11</t>
+          <t>comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Retorno mensal de bova11</t>
+          <t>metricCIF</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de bova11.</t>
+          <t>Valor mensal total das importações brasileiras em dólares CIF.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>US$ CIF</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -2613,71 +2593,67 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>^BVSP</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ret_ibovespa</t>
+          <t>comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Retorno mensal de ibovespa</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ibovespa.</t>
+          <t>Valor mensal total das importações brasileiras em dólares FOB.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -2690,71 +2666,67 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>IVVB11.SA</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ret_ivvb11</t>
+          <t>comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Retorno mensal de ivvb11</t>
+          <t>metricFreight</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ivvb11.</t>
+          <t>Valor mensal total do frete das importações brasileiras.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -2767,71 +2739,63 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SMAL11.SA</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ret_smal11</t>
+          <t>comex_importacoes_kg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Retorno mensal de smal11</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de smal11.</t>
+          <t>Peso líquido mensal total das importações brasileiras.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -2844,74 +2808,70 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SMAL11.SA</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>smal11</t>
+          <t>comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>smal11</t>
+          <t>metricInsurance</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ETF brasileiro associado ao segmento de small caps.</t>
+          <t>Valor mensal total do seguro das importações brasileiras.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>etf</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2921,17 +2881,13 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q40" t="b">
@@ -2941,43 +2897,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>^DJI</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>dow_jones</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>dow_jones</t>
-        </is>
-      </c>
+          <t>comex_saldo_comercial_usd</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Índice Dow Jones Industrial Average.</t>
+          <t>Saldo comercial mensal brasileiro.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2985,10 +2933,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2998,21 +2950,17 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>1997-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3029,37 +2977,37 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>^IXIC</t>
+          <t>BOVA11.SA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>nasdaq</t>
+          <t>bova11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>nasdaq</t>
+          <t>bova11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Índice Nasdaq Composite.</t>
+          <t>ETF brasileiro associado ao desempenho do Ibovespa.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>etf</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3100,49 +3048,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>^DJI</t>
+          <t>^BVSP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ret_dow_jones</t>
+          <t>ibovespa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Retorno mensal de dow_jones</t>
+          <t>ibovespa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de dow_jones.</t>
+          <t>Índice Ibovespa.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3152,7 +3100,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3166,7 +3114,7 @@
         </is>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3177,49 +3125,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>^IXIC</t>
+          <t>IVVB11.SA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ret_nasdaq</t>
+          <t>ivvb11</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Retorno mensal de nasdaq</t>
+          <t>ivvb11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de nasdaq.</t>
+          <t>ETF brasileiro com exposição ao índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>etf</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3229,7 +3177,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3243,7 +3191,7 @@
         </is>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3260,27 +3208,27 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>BOVA11.SA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ret_sp500</t>
+          <t>ret_bova11</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Retorno mensal de sp500</t>
+          <t>Retorno mensal de bova11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de sp500.</t>
+          <t>Retorno percentual mensal simples de bova11.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3331,49 +3279,49 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>^GSPC</t>
+          <t>^BVSP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>ret_ibovespa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>Retorno mensal de ibovespa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Retorno percentual mensal simples de ibovespa.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3383,7 +3331,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3397,7 +3345,7 @@
         </is>
       </c>
       <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3408,49 +3356,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BRL=X</t>
+          <t>IVVB11.SA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>dolar_real</t>
+          <t>ret_ivvb11</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>dolar_real</t>
+          <t>Retorno mensal de ivvb11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Taxa de câmbio R$/US$ aproximada pelo Yahoo Finance.</t>
+          <t>Retorno percentual mensal simples de ivvb11.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>BRL_por_USD</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3460,7 +3408,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3474,7 +3422,7 @@
         </is>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3485,49 +3433,49 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EURBRL=X</t>
+          <t>SMAL11.SA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>euro_real</t>
+          <t>ret_smal11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>euro_real</t>
+          <t>Retorno mensal de smal11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Taxa de câmbio R$/EUR aproximada pelo Yahoo Finance.</t>
+          <t>Retorno percentual mensal simples de smal11.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BRL_por_EUR</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3537,7 +3485,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3551,7 +3499,7 @@
         </is>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3562,49 +3510,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BRL=X</t>
+          <t>SMAL11.SA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ret_dolar_real</t>
+          <t>smal11</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Retorno mensal de dolar_real</t>
+          <t>smal11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de dolar_real.</t>
+          <t>ETF brasileiro associado ao segmento de small caps.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>bolsa_brasil</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>etf</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3614,7 +3562,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3628,7 +3576,7 @@
         </is>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3639,49 +3587,49 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EURBRL=X</t>
+          <t>^DJI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ret_euro_real</t>
+          <t>dow_jones</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Retorno mensal de euro_real</t>
+          <t>dow_jones</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de euro_real.</t>
+          <t>Índice Dow Jones Industrial Average.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3691,7 +3639,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3705,7 +3653,7 @@
         </is>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3722,32 +3670,32 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ZC=F</t>
+          <t>^IXIC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>milho</t>
+          <t>nasdaq</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>milho</t>
+          <t>nasdaq</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Contrato futuro de milho.</t>
+          <t>Índice Nasdaq Composite.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3793,49 +3741,49 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>^DJI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ouro</t>
+          <t>ret_dow_jones</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ouro</t>
+          <t>Retorno mensal de dow_jones</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Contrato futuro de ouro.</t>
+          <t>Retorno percentual mensal simples de dow_jones.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3845,7 +3793,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3859,7 +3807,7 @@
         </is>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3870,49 +3818,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^IXIC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>petroleo_brent</t>
+          <t>ret_nasdaq</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>petroleo_brent</t>
+          <t>Retorno mensal de nasdaq</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Contrato futuro de petróleo Brent.</t>
+          <t>Retorno percentual mensal simples de nasdaq.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3922,7 +3870,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3936,7 +3884,7 @@
         </is>
       </c>
       <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3947,49 +3895,49 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>petroleo_wti</t>
+          <t>ret_sp500</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>petroleo_wti</t>
+          <t>Retorno mensal de sp500</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Contrato futuro de petróleo WTI.</t>
+          <t>Retorno percentual mensal simples de sp500.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>retorno_mensal_pct</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>percentual</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3999,7 +3947,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>pct_change</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4013,7 +3961,7 @@
         </is>
       </c>
       <c r="Q54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4024,49 +3972,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ZC=F</t>
+          <t>^GSPC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ret_milho</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Retorno mensal de milho</t>
+          <t>sp500</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de milho.</t>
+          <t>Índice S&amp;P 500.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>bolsa_internacional</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>indice</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4076,7 +4024,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4090,7 +4038,7 @@
         </is>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4101,49 +4049,49 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>BRL=X</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ret_ouro</t>
+          <t>dolar_real</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Retorno mensal de ouro</t>
+          <t>dolar_real</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ouro.</t>
+          <t>Taxa de câmbio R$/US$ aproximada pelo Yahoo Finance.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>BRL_por_USD</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4153,7 +4101,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4167,7 +4115,7 @@
         </is>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4178,49 +4126,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>EURBRL=X</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ret_petroleo_brent</t>
+          <t>euro_real</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Retorno mensal de petroleo_brent</t>
+          <t>euro_real</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de petroleo_brent.</t>
+          <t>Taxa de câmbio R$/EUR aproximada pelo Yahoo Finance.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>percentual</t>
+          <t>BRL_por_EUR</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4230,7 +4178,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>pct_change</t>
+          <t>ultimo</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4244,7 +4192,7 @@
         </is>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4261,27 +4209,27 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CL=F</t>
+          <t>BRL=X</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ret_petroleo_wti</t>
+          <t>ret_dolar_real</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Retorno mensal de petroleo_wti</t>
+          <t>Retorno mensal de dolar_real</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de petroleo_wti.</t>
+          <t>Retorno percentual mensal simples de dolar_real.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4338,27 +4286,27 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>EURBRL=X</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ret_soja</t>
+          <t>ret_euro_real</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Retorno mensal de soja</t>
+          <t>Retorno mensal de euro_real</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de soja.</t>
+          <t>Retorno percentual mensal simples de euro_real.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4415,22 +4363,22 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ZS=F</t>
+          <t>ZC=F</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>milho</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>soja</t>
+          <t>milho</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Contrato futuro de soja.</t>
+          <t>Contrato futuro de milho.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4475,6 +4423,699 @@
         </is>
       </c>
       <c r="Q60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ouro</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ouro</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Contrato futuro de ouro.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BZ=F</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>petroleo_brent</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>petroleo_brent</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Contrato futuro de petróleo Brent.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CL=F</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>petroleo_wti</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>petroleo_wti</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Contrato futuro de petróleo WTI.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ZC=F</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ret_milho</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Retorno mensal de milho</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de milho.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ret_ouro</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Retorno mensal de ouro</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de ouro.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BZ=F</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ret_petroleo_brent</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Retorno mensal de petroleo_brent</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de petroleo_brent.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CL=F</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ret_petroleo_wti</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Retorno mensal de petroleo_wti</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de petroleo_wti.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ZS=F</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ret_soja</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Retorno mensal de soja</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de soja.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ZS=F</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>soja</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>soja</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Contrato futuro de soja.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q69" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
+++ b/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,7 +2384,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q33" t="b">
@@ -2457,7 +2457,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q34" t="b">
@@ -2526,7 +2526,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q35" t="b">
@@ -2599,7 +2599,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q36" t="b">
@@ -2672,7 +2672,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q37" t="b">
@@ -2745,7 +2745,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q38" t="b">
@@ -2814,7 +2814,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q39" t="b">
@@ -2887,7 +2887,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q40" t="b">
@@ -2909,13 +2909,17 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>comex_saldo_comercial_usd</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Saldo comercial mensal brasileiro.</t>
+          <t>Exportações brasileiras de Carnes desossadas de bovino, congeladas. para o mundo, NCM 02023000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2935,7 +2939,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>US$</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2956,64 +2960,60 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1997-01 até o último mês disponível</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BOVA11.SA</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>bova11</t>
+          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>bova11</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ETF brasileiro associado ao desempenho do Ibovespa.</t>
+          <t>Peso líquido das exportações brasileiras de Carnes desossadas de bovino, congeladas. para o mundo, NCM 02023000.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3023,17 +3023,13 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q42" t="b">
@@ -3043,54 +3039,54 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>^BVSP</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ibovespa</t>
+          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ibovespa</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Índice Ibovespa.</t>
+          <t>Importações brasileiras de Carnes desossadas de bovino, congeladas. provenientes do mundo, NCM 02023000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3100,17 +3096,13 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q43" t="b">
@@ -3120,54 +3112,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>IVVB11.SA</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ivvb11</t>
+          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ivvb11</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ETF brasileiro com exposição ao índice S&amp;P 500.</t>
+          <t>Peso líquido das importações brasileiras de Carnes desossadas de bovino, congeladas. provenientes do mundo, NCM 02023000.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3177,17 +3165,13 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q44" t="b">
@@ -3197,51 +3181,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BOVA11.SA</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ret_bova11</t>
+          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Retorno mensal de bova11</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de bova11.</t>
+          <t>Exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110, em dólares FOB.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3254,71 +3238,63 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>^BVSP</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ret_ibovespa</t>
+          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Retorno mensal de ibovespa</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ibovespa.</t>
+          <t>Peso líquido das exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3331,71 +3307,67 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>IVVB11.SA</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ret_ivvb11</t>
+          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Retorno mensal de ivvb11</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ivvb11.</t>
+          <t>Importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110, em dólares FOB.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3408,71 +3380,63 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SMAL11.SA</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ret_smal11</t>
+          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Retorno mensal de smal11</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de smal11.</t>
+          <t>Peso líquido das importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3485,74 +3449,70 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SMAL11.SA</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>smal11</t>
+          <t>comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>smal11</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ETF brasileiro associado ao segmento de small caps.</t>
+          <t>Exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>bolsa_brasil</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>etf</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3562,17 +3522,13 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q49" t="b">
@@ -3582,54 +3538,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>^DJI</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>dow_jones</t>
+          <t>comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>dow_jones</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Índice Dow Jones Industrial Average.</t>
+          <t>Peso líquido das exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>indice</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3639,17 +3591,13 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q50" t="b">
@@ -3659,43 +3607,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>^IXIC</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>nasdaq</t>
+          <t>comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>nasdaq</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Índice Nasdaq Composite.</t>
+          <t>Importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3703,10 +3647,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3716,17 +3664,13 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q51" t="b">
@@ -3736,51 +3680,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>^DJI</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ret_dow_jones</t>
+          <t>comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Retorno mensal de dow_jones</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de dow_jones.</t>
+          <t>Peso líquido das importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3793,71 +3733,67 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>^IXIC</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ret_nasdaq</t>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Retorno mensal de nasdaq</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de nasdaq.</t>
+          <t>Exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3870,71 +3806,63 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ret_sp500</t>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Retorno mensal de sp500</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de sp500.</t>
+          <t>Peso líquido das exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -3947,63 +3875,55 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>sp500</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Índice S&amp;P 500.</t>
+          <t>Importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>bolsa_internacional</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>indice</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4011,10 +3931,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4024,17 +3948,13 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q55" t="b">
@@ -4044,54 +3964,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BRL=X</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>dolar_real</t>
+          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>dolar_real</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Taxa de câmbio R$/US$ aproximada pelo Yahoo Finance.</t>
+          <t>Peso líquido das importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>cambio</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>BRL_por_USD</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4101,17 +4017,13 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q56" t="b">
@@ -4121,54 +4033,54 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>EURBRL=X</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>euro_real</t>
+          <t>comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>euro_real</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Taxa de câmbio R$/EUR aproximada pelo Yahoo Finance.</t>
+          <t>Exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400, em dólares FOB.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>BRL_por_EUR</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4178,17 +4090,13 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q57" t="b">
@@ -4198,51 +4106,47 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BRL=X</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ret_dolar_real</t>
+          <t>comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Retorno mensal de dolar_real</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de dolar_real.</t>
+          <t>Peso líquido das exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4255,71 +4159,67 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>EURBRL=X</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ret_euro_real</t>
+          <t>comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Retorno mensal de euro_real</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de euro_real.</t>
+          <t>Importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400, em dólares FOB.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4332,74 +4232,66 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ZC=F</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>milho</t>
+          <t>comex_ncm_17011400_acucares_cana_importacoes_kg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>milho</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Contrato futuro de milho.</t>
+          <t>Peso líquido das importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>futuro</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4409,17 +4301,13 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q60" t="b">
@@ -4429,43 +4317,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>GC=F</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ouro</t>
+          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ouro</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Contrato futuro de ouro.</t>
+          <t>Exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090, em dólares FOB.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4473,10 +4357,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4486,17 +4374,13 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q61" t="b">
@@ -4506,54 +4390,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BZ=F</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>petroleo_brent</t>
+          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>petroleo_brent</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Contrato futuro de petróleo Brent.</t>
+          <t>Peso líquido das exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>futuro</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4563,17 +4443,13 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q62" t="b">
@@ -4583,43 +4459,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yahoo Finance via yfinance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CL=F</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>petroleo_wti</t>
+          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>petroleo_wti</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Contrato futuro de petróleo WTI.</t>
+          <t>Importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090, em dólares FOB.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4627,10 +4499,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4640,17 +4516,13 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q63" t="b">
@@ -4660,51 +4532,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ZC=F</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ret_milho</t>
+          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Retorno mensal de milho</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de milho.</t>
+          <t>Peso líquido das importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4717,71 +4585,67 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>GC=F</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ret_ouro</t>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Retorno mensal de ouro</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de ouro.</t>
+          <t>Exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100, em dólares FOB.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4794,71 +4658,63 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>BZ=F</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ret_petroleo_brent</t>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Retorno mensal de petroleo_brent</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de petroleo_brent.</t>
+          <t>Peso líquido das exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4871,71 +4727,67 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>CL=F</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ret_petroleo_wti</t>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Retorno mensal de petroleo_wti</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de petroleo_wti.</t>
+          <t>Importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100, em dólares FOB.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
+          <t>valor_monetario</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -4948,71 +4800,63 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>comexstat</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Calculado pelo script a partir do Yahoo Finance</t>
+          <t>Comex Stat/MDIC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ZS=F</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ret_soja</t>
+          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Retorno mensal de soja</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Retorno percentual mensal simples de soja.</t>
+          <t>Peso líquido das importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>commodities</t>
+          <t>comercio_exterior</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>retorno_mensal_pct</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>percentual</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -5025,97 +4869,3093 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>pct_change</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>5y</t>
+          <t>2020-01 até o último mês disponível</t>
         </is>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Peso líquido das exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Peso líquido das importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Exportações brasileiras de Fuel oil. para o mundo, NCM 27101922, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Peso líquido das exportações brasileiras de Fuel oil. para o mundo, NCM 27101922.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Peso líquido das importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Peso líquido das exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900, em dólares FOB.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>US$ FOB</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Peso líquido das importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>kg líquido</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>comexstat</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Comex Stat/MDIC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>comex_saldo_comercial_usd</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Saldo comercial mensal brasileiro.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>valor mensal oficial</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2020-01 até o último mês disponível</t>
+        </is>
+      </c>
+      <c r="Q81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>yahoo</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Yahoo Finance via yfinance</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BOVA11.SA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>bova11</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>bova11</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ETF brasileiro associado ao desempenho do Ibovespa.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>^BVSP</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ibovespa</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ibovespa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Índice Ibovespa.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>IVVB11.SA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ivvb11</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ivvb11</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ETF brasileiro com exposição ao índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BOVA11.SA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ret_bova11</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Retorno mensal de bova11</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de bova11.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>^BVSP</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ret_ibovespa</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Retorno mensal de ibovespa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de ibovespa.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>IVVB11.SA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ret_ivvb11</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Retorno mensal de ivvb11</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de ivvb11.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SMAL11.SA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ret_smal11</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Retorno mensal de smal11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de smal11.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SMAL11.SA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>smal11</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>smal11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ETF brasileiro associado ao segmento de small caps.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>bolsa_brasil</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>etf</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>^DJI</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>dow_jones</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>dow_jones</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Índice Dow Jones Industrial Average.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>nasdaq</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>nasdaq</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Índice Nasdaq Composite.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>^DJI</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ret_dow_jones</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Retorno mensal de dow_jones</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de dow_jones.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ret_nasdaq</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Retorno mensal de nasdaq</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de nasdaq.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ret_sp500</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Retorno mensal de sp500</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de sp500.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>sp500</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Índice S&amp;P 500.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>bolsa_internacional</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BRL=X</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>dolar_real</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>dolar_real</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Taxa de câmbio R$/US$ aproximada pelo Yahoo Finance.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>BRL_por_USD</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EURBRL=X</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>euro_real</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>euro_real</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Taxa de câmbio R$/EUR aproximada pelo Yahoo Finance.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>BRL_por_EUR</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BRL=X</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ret_dolar_real</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Retorno mensal de dolar_real</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de dolar_real.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EURBRL=X</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ret_euro_real</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Retorno mensal de euro_real</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de euro_real.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>cambio</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ZC=F</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Contrato futuro de milho.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ouro</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ouro</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Contrato futuro de ouro.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BZ=F</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>petroleo_brent</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>petroleo_brent</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Contrato futuro de petróleo Brent.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CL=F</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>petroleo_wti</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>petroleo_wti</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Contrato futuro de petróleo WTI.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ZC=F</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ret_milho</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Retorno mensal de milho</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de milho.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ret_ouro</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Retorno mensal de ouro</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de ouro.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BZ=F</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ret_petroleo_brent</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Retorno mensal de petroleo_brent</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de petroleo_brent.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CL=F</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ret_petroleo_wti</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Retorno mensal de petroleo_wti</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de petroleo_wti.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Calculado pelo script a partir do Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
         <is>
           <t>ZS=F</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ret_soja</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Retorno mensal de soja</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Retorno percentual mensal simples de soja.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>retorno_mensal_pct</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>percentual</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>5y</t>
+        </is>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>yahoo</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Yahoo Finance via yfinance</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ZS=F</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>soja</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>soja</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Contrato futuro de soja.</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>commodities</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>futuro</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>ultimo</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P109" t="inlineStr">
         <is>
           <t>5y</t>
         </is>
       </c>
-      <c r="Q69" t="b">
+      <c r="Q109" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
+++ b/data/final/documentacao/dicionario_variaveis_consolidado.xlsx
@@ -2337,13 +2337,17 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>comex_corrente_comercio_usd</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>acucares_cana_exp_fob</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>metricFOB</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corrente mensal de comércio exterior brasileira.</t>
+          <t>Exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400, em dólares FOB.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2363,7 +2367,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>US$</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2388,7 +2392,7 @@
         </is>
       </c>
       <c r="Q33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2406,17 +2410,17 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>comex_exportacoes_fob_usd</t>
+          <t>acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Valor mensal total das exportações brasileiras em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2426,17 +2430,13 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2479,17 +2479,17 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>comex_exportacoes_kg</t>
+          <t>acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Peso líquido mensal total das exportações brasileiras.</t>
+          <t>Importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400, em dólares FOB.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2499,13 +2499,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2548,17 +2552,17 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>comex_importacoes_cif_usd</t>
+          <t>acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>metricCIF</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Valor mensal total das importações brasileiras em dólares CIF.</t>
+          <t>Peso líquido das importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2568,17 +2572,13 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>US$ CIF</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2621,7 +2621,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>comex_importacoes_fob_usd</t>
+          <t>cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Valor mensal total das importações brasileiras em dólares FOB.</t>
+          <t>Exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110, em dólares FOB.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2694,17 +2694,17 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>comex_importacoes_frete_usd</t>
+          <t>cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>metricFreight</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Valor mensal total do frete das importações brasileiras.</t>
+          <t>Peso líquido das exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2714,17 +2714,13 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>US$</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2767,17 +2763,17 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>comex_importacoes_kg</t>
+          <t>cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Peso líquido mensal total das importações brasileiras.</t>
+          <t>Importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110, em dólares FOB.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2787,13 +2783,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2836,17 +2836,17 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>comex_importacoes_seguro_usd</t>
+          <t>cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>metricInsurance</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Valor mensal total do seguro das importações brasileiras.</t>
+          <t>Peso líquido das importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2856,17 +2856,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>US$</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2909,7 +2905,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+          <t>carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2982,7 +2978,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+          <t>carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3051,7 +3047,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+          <t>carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3124,7 +3120,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+          <t>carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3193,7 +3189,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+          <t>celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3203,7 +3199,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110, em dólares FOB.</t>
+          <t>Exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900, em dólares FOB.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3266,7 +3262,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+          <t>celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3276,7 +3272,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Café não torrado, não descafeinado, em grão. para o mundo, NCM 09011110.</t>
+          <t>Peso líquido das exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3335,7 +3331,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+          <t>celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3345,7 +3341,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110, em dólares FOB.</t>
+          <t>Importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900, em dólares FOB.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3408,7 +3404,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+          <t>celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3418,7 +3414,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Café não torrado, não descafeinado, em grão. provenientes do mundo, NCM 09011110.</t>
+          <t>Peso líquido das importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3477,17 +3473,13 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>metricFOB</t>
-        </is>
-      </c>
+          <t>comex_corrente_comercio_usd</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010, em dólares FOB.</t>
+          <t>Corrente mensal de comércio exterior brasileira.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3507,7 +3499,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>US$</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3532,7 +3524,7 @@
         </is>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3550,17 +3542,17 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+          <t>comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010.</t>
+          <t>Valor mensal total das exportações brasileiras em dólares FOB.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3570,13 +3562,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3619,17 +3615,17 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+          <t>comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010, em dólares FOB.</t>
+          <t>Peso líquido mensal total das exportações brasileiras.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3639,17 +3635,13 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3692,17 +3684,17 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+          <t>comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricCIF</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010.</t>
+          <t>Valor mensal total das importações brasileiras em dólares CIF.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3712,13 +3704,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ CIF</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3761,7 +3757,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+          <t>comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000, em dólares FOB.</t>
+          <t>Valor mensal total das importações brasileiras em dólares FOB.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3834,17 +3830,17 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+          <t>comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFreight</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000.</t>
+          <t>Valor mensal total do frete das importações brasileiras.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3854,13 +3850,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3903,17 +3903,17 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+          <t>comex_importacoes_kg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000, em dólares FOB.</t>
+          <t>Peso líquido mensal total das importações brasileiras.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3923,17 +3923,13 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3976,17 +3972,17 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+          <t>comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricInsurance</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000.</t>
+          <t>Valor mensal total do seguro das importações brasileiras.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3996,13 +3992,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4045,17 +4045,13 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>metricFOB</t>
-        </is>
-      </c>
+          <t>comex_saldo_comercial_usd</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400, em dólares FOB.</t>
+          <t>Saldo comercial mensal brasileiro.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4075,7 +4071,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>US$</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4100,7 +4096,7 @@
         </is>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -4118,17 +4114,17 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+          <t>fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Outros açúcares de cana. para o mundo, NCM 17011400.</t>
+          <t>Exportações brasileiras de Fuel oil. para o mundo, NCM 27101922, em dólares FOB.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4138,13 +4134,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4187,17 +4187,17 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+          <t>fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Fuel oil. para o mundo, NCM 27101922.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4207,17 +4207,13 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4260,17 +4256,17 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+          <t>fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Outros açúcares de cana. provenientes do mundo, NCM 17011400.</t>
+          <t>Importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922, em dólares FOB.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4280,13 +4276,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4329,17 +4329,17 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+          <t>fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090, em dólares FOB.</t>
+          <t>Peso líquido das importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4349,17 +4349,13 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4402,17 +4398,17 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+          <t>milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090.</t>
+          <t>Exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4422,13 +4418,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4471,17 +4471,17 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+          <t>milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Milho em grão, exceto para semeadura. para o mundo, NCM 10059010.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4491,17 +4491,13 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4544,17 +4540,17 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+          <t>milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090.</t>
+          <t>Importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4564,13 +4560,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4613,17 +4613,17 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+          <t>milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100, em dólares FOB.</t>
+          <t>Peso líquido das importações brasileiras de Milho em grão, exceto para semeadura. provenientes do mundo, NCM 10059010.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4633,17 +4633,13 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4686,17 +4682,17 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+          <t>minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100.</t>
+          <t>Exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100, em dólares FOB.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4706,13 +4702,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4755,17 +4755,17 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+          <t>minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. para o mundo, NCM 26011100.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4775,17 +4775,13 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4828,17 +4824,17 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+          <t>minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100.</t>
+          <t>Importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100, em dólares FOB.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4848,13 +4844,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4897,17 +4897,17 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+          <t>minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010, em dólares FOB.</t>
+          <t>Peso líquido das importações brasileiras de Minérios de ferro e seus concentrados, não aglomerados. provenientes do mundo, NCM 26011100.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4917,17 +4917,13 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4970,17 +4966,17 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+          <t>oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010.</t>
+          <t>Exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4990,13 +4986,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5039,17 +5039,17 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+          <t>oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Óleos brutos de petróleo. para o mundo, NCM 27090010.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5059,17 +5059,13 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5112,17 +5108,17 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+          <t>oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010.</t>
+          <t>Importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010, em dólares FOB.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5132,13 +5128,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5181,17 +5181,17 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+          <t>oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Fuel oil. para o mundo, NCM 27101922, em dólares FOB.</t>
+          <t>Peso líquido das importações brasileiras de Óleos brutos de petróleo. provenientes do mundo, NCM 27090010.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5201,17 +5201,13 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5254,17 +5250,17 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+          <t>residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Fuel oil. para o mundo, NCM 27101922.</t>
+          <t>Exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090, em dólares FOB.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5274,13 +5270,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5323,17 +5323,17 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+          <t>residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. para o mundo, NCM 23040090.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5343,17 +5343,13 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5396,17 +5392,17 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+          <t>residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Fuel oil. provenientes do mundo, NCM 27101922.</t>
+          <t>Importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090, em dólares FOB.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5416,13 +5412,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5465,17 +5465,17 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+          <t>residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900, em dólares FOB.</t>
+          <t>Peso líquido das importações brasileiras de Bagaços e outros resíduos sólidos da extração do óleo de soja. provenientes do mundo, NCM 23040090.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5485,17 +5485,13 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5538,17 +5534,17 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+          <t>soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Peso líquido das exportações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. para o mundo, NCM 47032900.</t>
+          <t>Exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5558,13 +5554,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5607,17 +5607,17 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+          <t>soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>metricFOB</t>
+          <t>metricKG</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900, em dólares FOB.</t>
+          <t>Peso líquido das exportações brasileiras de Soja, mesmo triturada, exceto para semeadura. para o mundo, NCM 12019000.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5627,17 +5627,13 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>US$ FOB</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5680,17 +5676,17 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+          <t>soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>metricKG</t>
+          <t>metricFOB</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Peso líquido das importações brasileiras de Pastas químicas de madeira, semibranqueadas ou branqueadas, de não coníferas. provenientes do mundo, NCM 47032900.</t>
+          <t>Importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000, em dólares FOB.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5700,13 +5696,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>peso_liquido</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>valor_monetario</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>kg líquido</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5749,13 +5749,17 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>comex_saldo_comercial_usd</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>soja_exceto_semeadura_imp_kg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>metricKG</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Saldo comercial mensal brasileiro.</t>
+          <t>Peso líquido das importações brasileiras de Soja, mesmo triturada, exceto para semeadura. provenientes do mundo, NCM 12019000.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5765,17 +5769,13 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>valor_monetario</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>peso_liquido</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>US$</t>
+          <t>kg líquido</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
